--- a/Enertiv Product Management/25-asset-level-esg-data-NY.xlsx
+++ b/Enertiv Product Management/25-asset-level-esg-data-NY.xlsx
@@ -2369,6 +2369,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="26" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="14"/>
   </cols>
@@ -2464,6 +2465,11 @@
       <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t>12-Month Whole-Building Data Complete</t>
+        </is>
+      </c>
       <c r="AF1" s="3" t="s">
         <v>30</v>
       </c>
@@ -2561,6 +2567,11 @@
       <c r="AD2" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="AE2" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AF2" s="11" t="s">
         <v>43</v>
       </c>
@@ -2659,6 +2670,11 @@
       <c r="AD3" s="4" t="s">
         <v>52</v>
       </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AF3" s="12" t="s">
         <v>53</v>
       </c>
@@ -2759,6 +2775,11 @@
       <c r="AD4" s="4" t="s">
         <v>61</v>
       </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AF4" s="14" t="s">
         <v>62</v>
       </c>
@@ -2857,6 +2878,11 @@
       <c r="AD5" s="4" t="s">
         <v>71</v>
       </c>
+      <c r="AE5" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
@@ -2951,6 +2977,11 @@
       <c r="AD6" s="4" t="s">
         <v>81</v>
       </c>
+      <c r="AE6" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
@@ -3045,6 +3076,11 @@
       <c r="AD7" s="4" t="s">
         <v>88</v>
       </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
@@ -3139,6 +3175,11 @@
       <c r="AD8" s="4" t="s">
         <v>94</v>
       </c>
+      <c r="AE8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
@@ -3233,6 +3274,11 @@
       <c r="AD9" s="4" t="s">
         <v>100</v>
       </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
@@ -3327,6 +3373,11 @@
       <c r="AD10" s="4" t="s">
         <v>61</v>
       </c>
+      <c r="AE10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
@@ -3421,6 +3472,11 @@
       <c r="AD11" s="4" t="s">
         <v>111</v>
       </c>
+      <c r="AE11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
@@ -3515,6 +3571,11 @@
       <c r="AD12" s="4" t="s">
         <v>118</v>
       </c>
+      <c r="AE12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
@@ -3609,6 +3670,11 @@
       <c r="AD13" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="AE13" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
@@ -3703,6 +3769,11 @@
       <c r="AD14" s="4" t="s">
         <v>130</v>
       </c>
+      <c r="AE14" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -3797,6 +3868,11 @@
       <c r="AD15" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="AE15" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
@@ -3891,6 +3967,11 @@
       <c r="AD16" s="4" t="s">
         <v>141</v>
       </c>
+      <c r="AE16" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
@@ -3985,6 +4066,11 @@
       <c r="AD17" s="4" t="s">
         <v>147</v>
       </c>
+      <c r="AE17" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
@@ -4079,6 +4165,11 @@
       <c r="AD18" s="4" t="s">
         <v>154</v>
       </c>
+      <c r="AE18" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
@@ -4173,6 +4264,11 @@
       <c r="AD19" s="4" t="s">
         <v>160</v>
       </c>
+      <c r="AE19" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
@@ -4267,6 +4363,11 @@
       <c r="AD20" s="4" t="s">
         <v>166</v>
       </c>
+      <c r="AE20" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
@@ -4361,6 +4462,11 @@
       <c r="AD21" s="4" t="s">
         <v>173</v>
       </c>
+      <c r="AE21" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
@@ -4455,6 +4561,11 @@
       <c r="AD22" s="4" t="s">
         <v>130</v>
       </c>
+      <c r="AE22" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
@@ -4549,6 +4660,11 @@
       <c r="AD23" s="4" t="s">
         <v>184</v>
       </c>
+      <c r="AE23" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
@@ -4643,6 +4759,11 @@
       <c r="AD24" s="4" t="s">
         <v>190</v>
       </c>
+      <c r="AE24" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
@@ -4737,6 +4858,11 @@
       <c r="AD25" s="4" t="s">
         <v>196</v>
       </c>
+      <c r="AE25" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
@@ -4831,6 +4957,11 @@
       <c r="AD26" s="4" t="s">
         <v>202</v>
       </c>
+      <c r="AE26" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
@@ -4925,6 +5056,11 @@
       <c r="AD27" s="4" t="s">
         <v>209</v>
       </c>
+      <c r="AE27" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
@@ -5019,6 +5155,11 @@
       <c r="AD28" s="4" t="s">
         <v>215</v>
       </c>
+      <c r="AE28" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
@@ -5113,6 +5254,11 @@
       <c r="AD29" s="4" t="s">
         <v>221</v>
       </c>
+      <c r="AE29" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
@@ -5207,6 +5353,11 @@
       <c r="AD30" s="4" t="s">
         <v>227</v>
       </c>
+      <c r="AE30" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
@@ -5300,6 +5451,11 @@
       </c>
       <c r="AD31" s="4" t="s">
         <v>234</v>
+      </c>
+      <c r="AE31" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5380,9 +5536,13 @@
       <c r="AB33" s="15"/>
       <c r="AC33" s="15"/>
       <c r="AD33" s="15"/>
+      <c r="AE33" s="15" t="str">
+        <f aca="false">COUNTIF(AE2:AE31,"Y")&amp;" of "&amp;COUNTA(AE2:AE31)&amp;" complete"</f>
+        <v>22 of 30 complete</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD31"/>
+  <autoFilter ref="A1:AE31"/>
   <mergeCells count="2">
     <mergeCell ref="AF2:AG2"/>
     <mergeCell ref="AF4:AG4"/>
@@ -17249,7 +17409,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
@@ -17488,6 +17648,37 @@
       </c>
       <c r="B39" s="48" t="s">
         <v>509</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="47" t="inlineStr">
+        <is>
+          <t>ENERGY STAR eligibility - 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="49" t="inlineStr">
+        <is>
+          <t>12-Month Whole-Building Data Complete</t>
+        </is>
+      </c>
+      <c r="B42" s="48" t="inlineStr">
+        <is>
+          <t>Y/N per asset. ENERGY STAR certification requires 12 full consecutive months of whole-building data across all fuel types, which is a separate gate from the 1-100 score. Fabricated for prototyping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="49" t="inlineStr">
+        <is>
+          <t>Relationship to Data Coverage</t>
+        </is>
+      </c>
+      <c r="B43" s="48" t="inlineStr">
+        <is>
+          <t>Deliberately independent. Data Coverage (%) measures how much floor area / consumption is verified, for audit-defensibility. This flag asks whether a complete 12-month year exists at all. An asset can have high coverage and an incomplete year (NY-023, 93.8%, N), or low coverage and a complete one (NY-026, 48.2%, Y). Certification eligibility = score 75+ AND this flag.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Enertiv Product Management/25-asset-level-esg-data-NY.xlsx
+++ b/Enertiv Product Management/25-asset-level-esg-data-NY.xlsx
@@ -2535,7 +2535,7 @@
         <v>17444.1</v>
       </c>
       <c r="T2" s="7" t="n">
-        <v>212469</v>
+        <v>1980000</v>
       </c>
       <c r="U2" s="7" t="n">
         <v>19186</v>
@@ -2846,7 +2846,7 @@
         <v>196574.1</v>
       </c>
       <c r="T5" s="7" t="n">
-        <v>2367714</v>
+        <v>3089988</v>
       </c>
       <c r="U5" s="7" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
         <v>123121.8</v>
       </c>
       <c r="T6" s="7" t="n">
-        <v>1886979</v>
+        <v>2757078</v>
       </c>
       <c r="U6" s="7" t="n">
         <v>0</v>
@@ -3143,7 +3143,7 @@
         <v>55564.4</v>
       </c>
       <c r="T8" s="7" t="n">
-        <v>441890</v>
+        <v>1978020</v>
       </c>
       <c r="U8" s="7" t="n">
         <v>48513</v>
@@ -3638,7 +3638,7 @@
         <v>308634.4</v>
       </c>
       <c r="T13" s="7" t="n">
-        <v>3652482</v>
+        <v>4378752</v>
       </c>
       <c r="U13" s="7" t="n">
         <v>65682</v>
@@ -3836,7 +3836,7 @@
         <v>126417.8</v>
       </c>
       <c r="T15" s="7" t="n">
-        <v>2671026</v>
+        <v>5231520</v>
       </c>
       <c r="U15" s="7" t="n">
         <v>265789</v>
@@ -3935,7 +3935,7 @@
         <v>230191.4</v>
       </c>
       <c r="T16" s="7" t="n">
-        <v>2052829</v>
+        <v>3692520</v>
       </c>
       <c r="U16" s="7" t="n">
         <v>102710</v>
@@ -4034,7 +4034,7 @@
         <v>732936.5</v>
       </c>
       <c r="T17" s="7" t="n">
-        <v>5397694</v>
+        <v>6979005</v>
       </c>
       <c r="U17" s="7" t="n">
         <v>289701</v>
@@ -4232,7 +4232,7 @@
         <v>66392</v>
       </c>
       <c r="T19" s="7" t="n">
-        <v>341125</v>
+        <v>796320</v>
       </c>
       <c r="U19" s="7" t="n">
         <v>44876</v>
@@ -4727,7 +4727,7 @@
         <v>375112.6</v>
       </c>
       <c r="T24" s="7" t="n">
-        <v>4022033</v>
+        <v>4651020</v>
       </c>
       <c r="U24" s="7" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
         <v>459453.5</v>
       </c>
       <c r="T27" s="7" t="n">
-        <v>3940905</v>
+        <v>8239104</v>
       </c>
       <c r="U27" s="7" t="n">
         <v>0</v>
@@ -5321,7 +5321,7 @@
         <v>715834.4</v>
       </c>
       <c r="T30" s="7" t="n">
-        <v>4709928</v>
+        <v>6881760</v>
       </c>
       <c r="U30" s="7" t="n">
         <v>271138</v>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="H62" s="23" t="n">
         <f aca="false">'Asset-Level Data'!T2</f>
-        <v>212469</v>
+        <v>1980000</v>
       </c>
       <c r="I62" s="23" t="n">
         <f aca="false">F62*(1-$Q$5)</f>
@@ -8468,15 +8468,15 @@
       </c>
       <c r="K62" s="9" t="n">
         <f aca="false">(F62-H62)/(F62-I62)</f>
-        <v>2.05002948560333</v>
+        <v>-36.3558054</v>
       </c>
       <c r="L62" s="23" t="n">
         <f aca="false">H62-I62</f>
-        <v>-48324.94</v>
+        <v>1719206.06</v>
       </c>
       <c r="M62" s="4" t="str">
         <f aca="false">IF(K62&gt;=1,"Target Met",IF(K62&gt;=0.75,"On Track",IF(K62&gt;=0.4,"At Risk","Off Track")))</f>
-        <v>Target Met</v>
+        <v>Off Track</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="H65" s="23" t="n">
         <f aca="false">'Asset-Level Data'!T5</f>
-        <v>2367714</v>
+        <v>3089988</v>
       </c>
       <c r="I65" s="23" t="n">
         <f aca="false">F65*(1-$Q$5)</f>
@@ -8606,15 +8606,15 @@
       </c>
       <c r="K65" s="9" t="n">
         <f aca="false">(F65-H65)/(F65-I65)</f>
-        <v>1.82572417710981</v>
+        <v>0.3489888553</v>
       </c>
       <c r="L65" s="23" t="n">
         <f aca="false">H65-I65</f>
-        <v>-403863.235</v>
+        <v>318410.765</v>
       </c>
       <c r="M65" s="4" t="str">
         <f aca="false">IF(K65&gt;=1,"Target Met",IF(K65&gt;=0.75,"On Track",IF(K65&gt;=0.4,"At Risk","Off Track")))</f>
-        <v>Target Met</v>
+        <v>Off Track</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="H66" s="23" t="n">
         <f aca="false">'Asset-Level Data'!T6</f>
-        <v>1886979</v>
+        <v>2757078</v>
       </c>
       <c r="I66" s="23" t="n">
         <f aca="false">F66*(1-$Q$5)</f>
@@ -8652,15 +8652,15 @@
       </c>
       <c r="K66" s="9" t="n">
         <f aca="false">(F66-H66)/(F66-I66)</f>
-        <v>1.09064404354257</v>
+        <v>-1.480498353</v>
       </c>
       <c r="L66" s="23" t="n">
         <f aca="false">H66-I66</f>
-        <v>-30674.8049999997</v>
+        <v>839424.195</v>
       </c>
       <c r="M66" s="4" t="str">
         <f aca="false">IF(K66&gt;=1,"Target Met",IF(K66&gt;=0.75,"On Track",IF(K66&gt;=0.4,"At Risk","Off Track")))</f>
-        <v>Target Met</v>
+        <v>Off Track</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="H68" s="23" t="n">
         <f aca="false">'Asset-Level Data'!T8</f>
-        <v>441890</v>
+        <v>1978020</v>
       </c>
       <c r="I68" s="23" t="n">
         <f aca="false">F68*(1-$Q$5)</f>
@@ -8744,15 +8744,15 @@
       </c>
       <c r="K68" s="9" t="n">
         <f aca="false">(F68-H68)/(F68-I68)</f>
-        <v>0.928257680782316</v>
+        <v>-19.02001496</v>
       </c>
       <c r="L68" s="23" t="n">
         <f aca="false">H68-I68</f>
-        <v>5524.565</v>
+        <v>1541654.565</v>
       </c>
       <c r="M68" s="4" t="str">
         <f aca="false">IF(K68&gt;=1,"Target Met",IF(K68&gt;=0.75,"On Track",IF(K68&gt;=0.4,"At Risk","Off Track")))</f>
-        <v>On Track</v>
+        <v>Off Track</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="H73" s="23" t="n">
         <f aca="false">'Asset-Level Data'!T13</f>
-        <v>3652482</v>
+        <v>4378752</v>
       </c>
       <c r="I73" s="23" t="n">
         <f aca="false">F73*(1-$Q$5)</f>
@@ -8974,15 +8974,15 @@
       </c>
       <c r="K73" s="9" t="n">
         <f aca="false">(F73-H73)/(F73-I73)</f>
-        <v>1.30814503263477</v>
+        <v>0.2426412171</v>
       </c>
       <c r="L73" s="23" t="n">
         <f aca="false">H73-I73</f>
-        <v>-210038.19</v>
+        <v>516231.81</v>
       </c>
       <c r="M73" s="4" t="str">
         <f aca="false">IF(K73&gt;=1,"Target Met",IF(K73&gt;=0.75,"On Track",IF(K73&gt;=0.4,"At Risk","Off Track")))</f>
-        <v>Target Met</v>
+        <v>Off Track</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="H75" s="23" t="n">
         <f aca="false">'Asset-Level Data'!T15</f>
-        <v>2671026</v>
+        <v>5231520</v>
       </c>
       <c r="I75" s="23" t="n">
         <f aca="false">F75*(1-$Q$5)</f>
@@ -9066,15 +9066,15 @@
       </c>
       <c r="K75" s="9" t="n">
         <f aca="false">(F75-H75)/(F75-I75)</f>
-        <v>1.64776154077873</v>
+        <v>-3.163452001</v>
       </c>
       <c r="L75" s="23" t="n">
         <f aca="false">H75-I75</f>
-        <v>-344734.135</v>
+        <v>2215759.865</v>
       </c>
       <c r="M75" s="4" t="str">
         <f aca="false">IF(K75&gt;=1,"Target Met",IF(K75&gt;=0.75,"On Track",IF(K75&gt;=0.4,"At Risk","Off Track")))</f>
-        <v>Target Met</v>
+        <v>Off Track</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="H76" s="23" t="n">
         <f aca="false">'Asset-Level Data'!T16</f>
-        <v>2052829</v>
+        <v>3692520</v>
       </c>
       <c r="I76" s="23" t="n">
         <f aca="false">F76*(1-$Q$5)</f>
@@ -9112,15 +9112,15 @@
       </c>
       <c r="K76" s="9" t="n">
         <f aca="false">(F76-H76)/(F76-I76)</f>
-        <v>1.63130045190964</v>
+        <v>-2.390683193</v>
       </c>
       <c r="L76" s="23" t="n">
         <f aca="false">H76-I76</f>
-        <v>-257369.935</v>
+        <v>1382321.065</v>
       </c>
       <c r="M76" s="4" t="str">
         <f aca="false">IF(K76&gt;=1,"Target Met",IF(K76&gt;=0.75,"On Track",IF(K76&gt;=0.4,"At Risk","Off Track")))</f>
-        <v>Target Met</v>
+        <v>Off Track</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="H77" s="23" t="n">
         <f aca="false">'Asset-Level Data'!T17</f>
-        <v>5397694</v>
+        <v>6979005</v>
       </c>
       <c r="I77" s="23" t="n">
         <f aca="false">F77*(1-$Q$5)</f>
@@ -9158,15 +9158,15 @@
       </c>
       <c r="K77" s="9" t="n">
         <f aca="false">(F77-H77)/(F77-I77)</f>
-        <v>1.48610435730673</v>
+        <v>-0.03159563939</v>
       </c>
       <c r="L77" s="23" t="n">
         <f aca="false">H77-I77</f>
-        <v>-506478.335</v>
+        <v>1074832.665</v>
       </c>
       <c r="M77" s="4" t="str">
         <f aca="false">IF(K77&gt;=1,"Target Met",IF(K77&gt;=0.75,"On Track",IF(K77&gt;=0.4,"At Risk","Off Track")))</f>
-        <v>Target Met</v>
+        <v>Off Track</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="H79" s="23" t="n">
         <f aca="false">'Asset-Level Data'!T19</f>
-        <v>341125</v>
+        <v>796320</v>
       </c>
       <c r="I79" s="23" t="n">
         <f aca="false">F79*(1-$Q$5)</f>
@@ -9250,15 +9250,15 @@
       </c>
       <c r="K79" s="9" t="n">
         <f aca="false">(F79-H79)/(F79-I79)</f>
-        <v>2.01573470443285</v>
+        <v>-4.190438911</v>
       </c>
       <c r="L79" s="23" t="n">
         <f aca="false">H79-I79</f>
-        <v>-74499.585</v>
+        <v>380695.415</v>
       </c>
       <c r="M79" s="4" t="str">
         <f aca="false">IF(K79&gt;=1,"Target Met",IF(K79&gt;=0.75,"On Track",IF(K79&gt;=0.4,"At Risk","Off Track")))</f>
-        <v>Target Met</v>
+        <v>Off Track</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="H84" s="23" t="n">
         <f aca="false">'Asset-Level Data'!T24</f>
-        <v>4022033</v>
+        <v>4651020</v>
       </c>
       <c r="I84" s="23" t="n">
         <f aca="false">F84*(1-$Q$5)</f>
@@ -9480,15 +9480,15 @@
       </c>
       <c r="K84" s="9" t="n">
         <f aca="false">(F84-H84)/(F84-I84)</f>
-        <v>1.70686086453071</v>
+        <v>0.9312199456</v>
       </c>
       <c r="L84" s="23" t="n">
         <f aca="false">H84-I84</f>
-        <v>-573211.5</v>
+        <v>55775.5</v>
       </c>
       <c r="M84" s="4" t="str">
         <f aca="false">IF(K84&gt;=1,"Target Met",IF(K84&gt;=0.75,"On Track",IF(K84&gt;=0.4,"At Risk","Off Track")))</f>
-        <v>Target Met</v>
+        <v>On Track</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="H87" s="23" t="n">
         <f aca="false">'Asset-Level Data'!T27</f>
-        <v>3940905</v>
+        <v>8239104</v>
       </c>
       <c r="I87" s="23" t="n">
         <f aca="false">F87*(1-$Q$5)</f>
@@ -9618,15 +9618,15 @@
       </c>
       <c r="K87" s="9" t="n">
         <f aca="false">(F87-H87)/(F87-I87)</f>
-        <v>1.15914574264868</v>
+        <v>-4.847703174</v>
       </c>
       <c r="L87" s="23" t="n">
         <f aca="false">H87-I87</f>
-        <v>-113876.69</v>
+        <v>4184322.31</v>
       </c>
       <c r="M87" s="4" t="str">
         <f aca="false">IF(K87&gt;=1,"Target Met",IF(K87&gt;=0.75,"On Track",IF(K87&gt;=0.4,"At Risk","Off Track")))</f>
-        <v>Target Met</v>
+        <v>Off Track</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="H90" s="23" t="n">
         <f aca="false">'Asset-Level Data'!T30</f>
-        <v>4709928</v>
+        <v>6881760</v>
       </c>
       <c r="I90" s="23" t="n">
         <f aca="false">F90*(1-$Q$5)</f>
@@ -9756,15 +9756,15 @@
       </c>
       <c r="K90" s="9" t="n">
         <f aca="false">(F90-H90)/(F90-I90)</f>
-        <v>1.92768665775574</v>
+        <v>-0.2575417429</v>
       </c>
       <c r="L90" s="23" t="n">
         <f aca="false">H90-I90</f>
-        <v>-921999.534999999</v>
+        <v>1249832.465</v>
       </c>
       <c r="M90" s="4" t="str">
         <f aca="false">IF(K90&gt;=1,"Target Met",IF(K90&gt;=0.75,"On Track",IF(K90&gt;=0.4,"At Risk","Off Track")))</f>
-        <v>Target Met</v>
+        <v>Off Track</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
